--- a/ss.xlsx
+++ b/ss.xlsx
@@ -1,27 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PDAC_liver_metastasis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{409A1F48-14F6-41B1-990F-E34246737599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C699801-1D07-4D05-966F-41B5FE8BF9AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-4368" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38304" yWindow="-4260" windowWidth="15552" windowHeight="16656" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="31">
   <si>
     <t>sample_id</t>
   </si>
@@ -68,13 +69,52 @@
     <t>seurat_cluster</t>
   </si>
   <si>
-    <t>cell_type</t>
-  </si>
-  <si>
     <t>MOM</t>
   </si>
   <si>
     <t>KC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOM </t>
+  </si>
+  <si>
+    <t>MOM_2</t>
+  </si>
+  <si>
+    <t>MOM_3</t>
+  </si>
+  <si>
+    <t>MOM_6</t>
+  </si>
+  <si>
+    <t>KC_or_MOM</t>
+  </si>
+  <si>
+    <t>alpha_name</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>KC_or_MOM_mapp</t>
   </si>
 </sst>
 </file>
@@ -452,19 +492,154 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD2CB0D5-E3F8-4E19-B34B-F54DC41D3E17}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.88671875" customWidth="1"/>
     <col min="2" max="2" width="19.44140625" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABFE0982-A105-48BB-AF98-38E70F89ACBD}">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.88671875" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>14</v>
       </c>
       <c r="B1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -472,7 +647,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -480,7 +655,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -488,7 +663,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -496,7 +671,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -504,7 +679,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -512,7 +687,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -520,31 +695,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/ss.xlsx
+++ b/ss.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PDAC_liver_metastasis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C699801-1D07-4D05-966F-41B5FE8BF9AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA4AD1B5-56EF-469A-958C-4F1EE5189010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38304" yWindow="-4260" windowWidth="15552" windowHeight="16656" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -114,7 +114,7 @@
     <t>G</t>
   </si>
   <si>
-    <t>KC_or_MOM_mapp</t>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
